--- a/data/tuning COM translasi pitch.xlsx
+++ b/data/tuning COM translasi pitch.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.099</v>
+        <v>0.119</v>
       </c>
       <c r="C2" t="n">
-        <v>-11.788</v>
+        <v>-10.988</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>195.566</v>
+        <v>189.973</v>
       </c>
       <c r="F2" t="n">
-        <v>23.883</v>
+        <v>19.754</v>
       </c>
       <c r="G2" t="n">
-        <v>-35.451</v>
+        <v>-36.055</v>
       </c>
       <c r="H2" t="n">
-        <v>195.041</v>
+        <v>189.945</v>
       </c>
     </row>
     <row r="3">
@@ -496,25 +496,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>109.2</v>
+        <v>609.927</v>
       </c>
       <c r="C3" t="n">
-        <v>-11.788</v>
+        <v>-10.988</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>195.566</v>
+        <v>189.973</v>
       </c>
       <c r="F3" t="n">
-        <v>18.805</v>
+        <v>-4.929</v>
       </c>
       <c r="G3" t="n">
-        <v>-35.42</v>
+        <v>-36.071</v>
       </c>
       <c r="H3" t="n">
-        <v>196.784</v>
+        <v>189.513</v>
       </c>
     </row>
     <row r="4">
@@ -522,25 +522,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>219.936</v>
+        <v>1218.342</v>
       </c>
       <c r="C4" t="n">
-        <v>-11.788</v>
+        <v>-10.988</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>195.566</v>
+        <v>189.973</v>
       </c>
       <c r="F4" t="n">
-        <v>12.626</v>
+        <v>-1.349</v>
       </c>
       <c r="G4" t="n">
-        <v>-35.454</v>
+        <v>-36.049</v>
       </c>
       <c r="H4" t="n">
-        <v>194.854</v>
+        <v>190.769</v>
       </c>
     </row>
     <row r="5">
@@ -548,25 +548,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>332.07</v>
+        <v>1823.838</v>
       </c>
       <c r="C5" t="n">
-        <v>-11.788</v>
+        <v>-10.988</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>195.566</v>
+        <v>189.973</v>
       </c>
       <c r="F5" t="n">
-        <v>10.135</v>
+        <v>-9.246</v>
       </c>
       <c r="G5" t="n">
-        <v>-35.451</v>
+        <v>-36.053</v>
       </c>
       <c r="H5" t="n">
-        <v>195.042</v>
+        <v>190.564</v>
       </c>
     </row>
     <row r="6">
@@ -574,389 +574,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>444.965</v>
+        <v>2433.791</v>
       </c>
       <c r="C6" t="n">
-        <v>-11.788</v>
+        <v>-10.988</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>195.566</v>
+        <v>189.973</v>
       </c>
       <c r="F6" t="n">
-        <v>4.811</v>
+        <v>-11.139</v>
       </c>
       <c r="G6" t="n">
-        <v>-35.446</v>
+        <v>-36.051</v>
       </c>
       <c r="H6" t="n">
-        <v>195.328</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>556.133</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-35.435</v>
-      </c>
-      <c r="H7" t="n">
-        <v>195.924</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>668.125</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-4.696</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-35.436</v>
-      </c>
-      <c r="H8" t="n">
-        <v>195.903</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>780.0839999999999</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-6.038</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-35.429</v>
-      </c>
-      <c r="H9" t="n">
-        <v>196.314</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="n">
-        <v>892.237</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-5.114</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-35.425</v>
-      </c>
-      <c r="H10" t="n">
-        <v>196.547</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1003.979</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-2.261</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-35.424</v>
-      </c>
-      <c r="H11" t="n">
-        <v>196.589</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1116.071</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-35.422</v>
-      </c>
-      <c r="H12" t="n">
-        <v>196.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1228.213</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-7.967</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-35.426</v>
-      </c>
-      <c r="H13" t="n">
-        <v>196.455</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1340.326</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-10.482</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-35.428</v>
-      </c>
-      <c r="H14" t="n">
-        <v>196.341</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>1452.298</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-10.482</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-35.428</v>
-      </c>
-      <c r="H15" t="n">
-        <v>196.341</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>1564.033</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-9.898</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-35.424</v>
-      </c>
-      <c r="H16" t="n">
-        <v>196.562</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1678.276</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-9.308999999999999</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-35.421</v>
-      </c>
-      <c r="H17" t="n">
-        <v>196.772</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1788.196</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-9.308999999999999</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-35.421</v>
-      </c>
-      <c r="H18" t="n">
-        <v>196.772</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>1900.246</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-9.308999999999999</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-35.421</v>
-      </c>
-      <c r="H19" t="n">
-        <v>196.772</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>2012.524</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-11.788</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>195.566</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-9.308999999999999</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-35.421</v>
-      </c>
-      <c r="H20" t="n">
-        <v>196.772</v>
+        <v>190.667</v>
       </c>
     </row>
   </sheetData>

--- a/data/tuning COM translasi pitch.xlsx
+++ b/data/tuning COM translasi pitch.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,16 +464,26 @@
           <t>COMz</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.119</v>
+        <v>0.118</v>
       </c>
       <c r="C2" t="n">
-        <v>-10.988</v>
+        <v>-10.986</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -482,13 +492,19 @@
         <v>189.973</v>
       </c>
       <c r="F2" t="n">
-        <v>19.754</v>
+        <v>15.557</v>
       </c>
       <c r="G2" t="n">
-        <v>-36.055</v>
+        <v>-36.05</v>
       </c>
       <c r="H2" t="n">
-        <v>189.945</v>
+        <v>190.291</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.578551540067436</v>
       </c>
     </row>
     <row r="3">
@@ -496,10 +512,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>609.927</v>
+        <v>129.557</v>
       </c>
       <c r="C3" t="n">
-        <v>-10.988</v>
+        <v>-10.986</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -508,13 +524,19 @@
         <v>189.973</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.929</v>
+        <v>10.944</v>
       </c>
       <c r="G3" t="n">
-        <v>-36.071</v>
+        <v>-36.036</v>
       </c>
       <c r="H3" t="n">
-        <v>189.513</v>
+        <v>191.512</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8634394161242739</v>
       </c>
     </row>
     <row r="4">
@@ -522,10 +544,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1218.342</v>
+        <v>255.748</v>
       </c>
       <c r="C4" t="n">
-        <v>-10.988</v>
+        <v>-10.986</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -534,13 +556,19 @@
         <v>189.973</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.349</v>
+        <v>6.345</v>
       </c>
       <c r="G4" t="n">
-        <v>-36.049</v>
+        <v>-36.073</v>
       </c>
       <c r="H4" t="n">
-        <v>190.769</v>
+        <v>189.362</v>
+      </c>
+      <c r="I4" t="n">
+        <v>33.998667</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.978628634689978</v>
       </c>
     </row>
     <row r="5">
@@ -548,10 +576,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1823.838</v>
+        <v>383.642</v>
       </c>
       <c r="C5" t="n">
-        <v>-10.988</v>
+        <v>-10.986</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -560,13 +588,19 @@
         <v>189.973</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.246</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="n">
-        <v>-36.053</v>
+        <v>-36.057</v>
       </c>
       <c r="H5" t="n">
-        <v>190.564</v>
+        <v>190.245</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8978447447210421</v>
       </c>
     </row>
     <row r="6">
@@ -574,10 +608,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2433.791</v>
+        <v>511.874</v>
       </c>
       <c r="C6" t="n">
-        <v>-10.988</v>
+        <v>-10.986</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -586,13 +620,325 @@
         <v>189.973</v>
       </c>
       <c r="F6" t="n">
-        <v>-11.139</v>
+        <v>-4.757</v>
       </c>
       <c r="G6" t="n">
+        <v>-36.058</v>
+      </c>
+      <c r="H6" t="n">
+        <v>190.276</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>639.614</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-10.986</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-9.391</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-36.057</v>
+      </c>
+      <c r="H7" t="n">
+        <v>190.34</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>770.17</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-10.986</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-8.034000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-36.049</v>
+      </c>
+      <c r="H8" t="n">
+        <v>190.831</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>895.6799999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-10.986</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-7.525</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-36.045</v>
+      </c>
+      <c r="H9" t="n">
+        <v>191.048</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1023.369</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-10.986</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-7.525</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-36.045</v>
+      </c>
+      <c r="H10" t="n">
+        <v>191.048</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1151.743</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-10.986</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-7.525</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-36.045</v>
+      </c>
+      <c r="H11" t="n">
+        <v>191.048</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1279.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-10.986</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-10.281</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-36.047</v>
+      </c>
+      <c r="H12" t="n">
+        <v>190.916</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1408.008</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-10.986</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-10.432</v>
+      </c>
+      <c r="G13" t="n">
         <v>-36.051</v>
       </c>
-      <c r="H6" t="n">
-        <v>190.667</v>
+      <c r="H13" t="n">
+        <v>190.72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1535.435</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-10.986</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-9.927</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-36.047</v>
+      </c>
+      <c r="H14" t="n">
+        <v>190.94</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1663.366</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-10.986</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-9.927</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-36.047</v>
+      </c>
+      <c r="H15" t="n">
+        <v>190.94</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1793.033</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-10.986</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-9.927</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-36.047</v>
+      </c>
+      <c r="H16" t="n">
+        <v>190.94</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1919.378</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-10.986</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-9.927</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-36.047</v>
+      </c>
+      <c r="H17" t="n">
+        <v>190.94</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2047.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-10.986</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-9.927</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-36.047</v>
+      </c>
+      <c r="H18" t="n">
+        <v>190.94</v>
       </c>
     </row>
   </sheetData>

--- a/data/tuning COM translasi pitch.xlsx
+++ b/data/tuning COM translasi pitch.xlsx
@@ -480,31 +480,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.118</v>
+        <v>0.11</v>
       </c>
       <c r="C2" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F2" t="n">
-        <v>15.557</v>
+        <v>15.709</v>
       </c>
       <c r="G2" t="n">
-        <v>-36.05</v>
+        <v>-35.521</v>
       </c>
       <c r="H2" t="n">
-        <v>190.291</v>
+        <v>190.938</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>4.578551540067436</v>
+        <v>4.57855154006743</v>
       </c>
     </row>
     <row r="3">
@@ -512,31 +512,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>129.557</v>
+        <v>131.594</v>
       </c>
       <c r="C3" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F3" t="n">
-        <v>10.944</v>
+        <v>11.084</v>
       </c>
       <c r="G3" t="n">
-        <v>-36.036</v>
+        <v>-35.499</v>
       </c>
       <c r="H3" t="n">
-        <v>191.512</v>
+        <v>192.161</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8634394161242739</v>
+        <v>0.8634394161242734</v>
       </c>
     </row>
     <row r="4">
@@ -544,31 +544,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>255.748</v>
+        <v>255.009</v>
       </c>
       <c r="C4" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F4" t="n">
-        <v>6.345</v>
+        <v>9.106</v>
       </c>
       <c r="G4" t="n">
-        <v>-36.073</v>
+        <v>-35.54</v>
       </c>
       <c r="H4" t="n">
-        <v>189.362</v>
+        <v>189.867</v>
       </c>
       <c r="I4" t="n">
-        <v>33.998667</v>
+        <v>57.99946458667</v>
       </c>
       <c r="J4" t="n">
-        <v>5.978628634689978</v>
+        <v>6.450807674052801</v>
       </c>
     </row>
     <row r="5">
@@ -576,31 +576,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>383.642</v>
+        <v>384.395</v>
       </c>
       <c r="C5" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>-36.057</v>
+        <v>-35.521</v>
       </c>
       <c r="H5" t="n">
-        <v>190.245</v>
+        <v>190.923</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3256</v>
+        <v>0.3859</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8978447447210421</v>
+        <v>0.9371354365604985</v>
       </c>
     </row>
     <row r="6">
@@ -608,25 +608,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>511.874</v>
+        <v>510.762</v>
       </c>
       <c r="C6" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.757</v>
+        <v>-2.002</v>
       </c>
       <c r="G6" t="n">
-        <v>-36.058</v>
+        <v>-35.52</v>
       </c>
       <c r="H6" t="n">
-        <v>190.276</v>
+        <v>190.975</v>
       </c>
     </row>
     <row r="7">
@@ -634,25 +634,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>639.614</v>
+        <v>641.206</v>
       </c>
       <c r="C7" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F7" t="n">
-        <v>-9.391</v>
+        <v>-6.646</v>
       </c>
       <c r="G7" t="n">
-        <v>-36.057</v>
+        <v>-35.518</v>
       </c>
       <c r="H7" t="n">
-        <v>190.34</v>
+        <v>191.12</v>
       </c>
     </row>
     <row r="8">
@@ -660,25 +660,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>770.17</v>
+        <v>766.857</v>
       </c>
       <c r="C8" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.034000000000001</v>
+        <v>-8.538</v>
       </c>
       <c r="G8" t="n">
-        <v>-36.049</v>
+        <v>-35.515</v>
       </c>
       <c r="H8" t="n">
-        <v>190.831</v>
+        <v>191.268</v>
       </c>
     </row>
     <row r="9">
@@ -686,25 +686,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>895.6799999999999</v>
+        <v>895.251</v>
       </c>
       <c r="C9" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.525</v>
+        <v>-5.256</v>
       </c>
       <c r="G9" t="n">
-        <v>-36.045</v>
+        <v>-35.509</v>
       </c>
       <c r="H9" t="n">
-        <v>191.048</v>
+        <v>191.587</v>
       </c>
     </row>
     <row r="10">
@@ -712,25 +712,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1023.369</v>
+        <v>1023.012</v>
       </c>
       <c r="C10" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.525</v>
+        <v>-7.502</v>
       </c>
       <c r="G10" t="n">
-        <v>-36.045</v>
+        <v>-35.507</v>
       </c>
       <c r="H10" t="n">
-        <v>191.048</v>
+        <v>191.712</v>
       </c>
     </row>
     <row r="11">
@@ -738,25 +738,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1151.743</v>
+        <v>1150.749</v>
       </c>
       <c r="C11" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.525</v>
+        <v>-7.502</v>
       </c>
       <c r="G11" t="n">
-        <v>-36.045</v>
+        <v>-35.507</v>
       </c>
       <c r="H11" t="n">
-        <v>191.048</v>
+        <v>191.712</v>
       </c>
     </row>
     <row r="12">
@@ -764,25 +764,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1279.8</v>
+        <v>1278.83</v>
       </c>
       <c r="C12" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.281</v>
+        <v>-10.269</v>
       </c>
       <c r="G12" t="n">
-        <v>-36.047</v>
+        <v>-35.51</v>
       </c>
       <c r="H12" t="n">
-        <v>190.916</v>
+        <v>191.58</v>
       </c>
     </row>
     <row r="13">
@@ -790,25 +790,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1408.008</v>
+        <v>1406.997</v>
       </c>
       <c r="C13" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F13" t="n">
         <v>-10.432</v>
       </c>
       <c r="G13" t="n">
-        <v>-36.051</v>
+        <v>-35.513</v>
       </c>
       <c r="H13" t="n">
-        <v>190.72</v>
+        <v>191.383</v>
       </c>
     </row>
     <row r="14">
@@ -816,25 +816,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1535.435</v>
+        <v>1535.071</v>
       </c>
       <c r="C14" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.927</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-36.047</v>
+        <v>-35.51</v>
       </c>
       <c r="H14" t="n">
-        <v>190.94</v>
+        <v>191.548</v>
       </c>
     </row>
     <row r="15">
@@ -842,25 +842,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1663.366</v>
+        <v>1662.76</v>
       </c>
       <c r="C15" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.927</v>
+        <v>-10.269</v>
       </c>
       <c r="G15" t="n">
-        <v>-36.047</v>
+        <v>-35.51</v>
       </c>
       <c r="H15" t="n">
-        <v>190.94</v>
+        <v>191.58</v>
       </c>
     </row>
     <row r="16">
@@ -868,25 +868,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1793.033</v>
+        <v>1795.867</v>
       </c>
       <c r="C16" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F16" t="n">
-        <v>-9.927</v>
+        <v>-10.269</v>
       </c>
       <c r="G16" t="n">
-        <v>-36.047</v>
+        <v>-35.51</v>
       </c>
       <c r="H16" t="n">
-        <v>190.94</v>
+        <v>191.58</v>
       </c>
     </row>
     <row r="17">
@@ -894,25 +894,25 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1919.378</v>
+        <v>1934.668</v>
       </c>
       <c r="C17" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.927</v>
+        <v>-10.269</v>
       </c>
       <c r="G17" t="n">
-        <v>-36.047</v>
+        <v>-35.51</v>
       </c>
       <c r="H17" t="n">
-        <v>190.94</v>
+        <v>191.58</v>
       </c>
     </row>
     <row r="18">
@@ -920,25 +920,25 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2047.5</v>
+        <v>2063.293</v>
       </c>
       <c r="C18" t="n">
-        <v>-10.986</v>
+        <v>-8.93</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>189.973</v>
+        <v>190.77</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.927</v>
+        <v>-10.269</v>
       </c>
       <c r="G18" t="n">
-        <v>-36.047</v>
+        <v>-35.51</v>
       </c>
       <c r="H18" t="n">
-        <v>190.94</v>
+        <v>191.58</v>
       </c>
     </row>
   </sheetData>
